--- a/docs/CAS_LEADS_RESTORE_2026-05-09.xlsx
+++ b/docs/CAS_LEADS_RESTORE_2026-05-09.xlsx
@@ -5,7 +5,8 @@
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Lead Field Coverage" sheetId="2" r:id="rId2"/>
-    <sheet name="Still Missing (sample)" sheetId="3" r:id="rId3"/>
+    <sheet name="Still Missing" sheetId="3" r:id="rId3"/>
+    <sheet name="Truncated" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -399,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -470,7 +471,7 @@
         <v>Subspecialty on Leads BEFORE backfill</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -483,31 +484,63 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Subspecialty patched (SSOT v6)</v>
+        <v>Source SSOT v6 (used)</v>
       </c>
       <c r="B11">
-        <v>201</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Subspecialty truncated to 50 chars</v>
+        <v>Source MS Forms - CAS YES (used)</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Leads w/o Subspecialty (no SSOT email match)</v>
+        <v>Source MS Forms - CAS NO (used)</v>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Source MS Forms - CANN (used)</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Leads still missing Subspecialty</v>
+      </c>
+      <c r="B15">
         <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Cross-source conflicts (SSOT kept)</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Values truncated to 50 chars</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -777,7 +810,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B74"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -987,9 +1020,489 @@
         <v>rohini.charan@fraserhealth.ca</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>6999043000002343443</v>
+      </c>
+      <c r="B27" t="str">
+        <v>deb.bosley1@gmail.com</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>6999043000002343436</v>
+      </c>
+      <c r="B28" t="str">
+        <v>jaime.cox@albertahealthservices.ca</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>6999043000002343430</v>
+      </c>
+      <c r="B29" t="str">
+        <v>diannekirkpatrick21@gmail.com</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>6999043000002343429</v>
+      </c>
+      <c r="B30" t="str">
+        <v>reanne.booker@cancercarealberta.ca</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>6999043000002343428</v>
+      </c>
+      <c r="B31" t="str">
+        <v>monamahal2@gmail.com</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>6999043000002343427</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Lianne.yeager@saskhealthauthority.ca</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>6999043000002343426</v>
+      </c>
+      <c r="B33" t="str">
+        <v>andrew.cowan@bccancer.bc.ca</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>6999043000002343425</v>
+      </c>
+      <c r="B34" t="str">
+        <v>jonathan.isenberg@bccancer.bc.ca</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>6999043000002343419</v>
+      </c>
+      <c r="B35" t="str">
+        <v>jane.smith@hospital.ca</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>6999043000002343412</v>
+      </c>
+      <c r="B36" t="str">
+        <v>deb.shields@albertahealthservices.ca</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>6999043000002343409</v>
+      </c>
+      <c r="B37" t="str">
+        <v>kelly.yurasek@ucalgary.ca</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>6999043000002343407</v>
+      </c>
+      <c r="B38" t="str">
+        <v>joshua.nurkowski@saskhealthauthority.ca</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>6999043000002343406</v>
+      </c>
+      <c r="B39" t="str">
+        <v>tara.evans@albertahealthservices.ca</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>6999043000002343405</v>
+      </c>
+      <c r="B40" t="str">
+        <v>llemay@sbgh.mb.ca</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>6999043000002343404</v>
+      </c>
+      <c r="B41" t="str">
+        <v>clayton.young@saskhealthauthority.ca</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>6999043000002343403</v>
+      </c>
+      <c r="B42" t="str">
+        <v>kgelineau@sbgh.mb.ca</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>6999043000002343402</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Cara.Wihlidal@saskhealthauthority.ca</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>6999043000002343401</v>
+      </c>
+      <c r="B44" t="str">
+        <v>karen.rowles@albertahealthservices.ca</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>6999043000002343400</v>
+      </c>
+      <c r="B45" t="str">
+        <v>meg.vossen-anweiler@saskhealthauthority.ca</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>6999043000002343395</v>
+      </c>
+      <c r="B46" t="str">
+        <v>jveenhuy@ucalgary.ca</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>6999043000002343394</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Adriane.Stoeber@saskhealthauthority.ca</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>6999043000002343385</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Jpeters2@sbgh.mb.ca</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>6999043000002343382</v>
+      </c>
+      <c r="B49" t="str">
+        <v>danielle.murray@phc.ca</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>6999043000002343381</v>
+      </c>
+      <c r="B50" t="str">
+        <v>valerie.fontaine.chum@ssss.gouv.qc.ca</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>6999043000002343380</v>
+      </c>
+      <c r="B51" t="str">
+        <v>kturner@ottawaheart.ca</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>6999043000002343379</v>
+      </c>
+      <c r="B52" t="str">
+        <v>danielle.murray@pch.ca</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>6999043000002343378</v>
+      </c>
+      <c r="B53" t="str">
+        <v>emilie.theberge@ubc.ca</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>6999043000002343377</v>
+      </c>
+      <c r="B54" t="str">
+        <v>glister@shaw.ca</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>6999043000002343376</v>
+      </c>
+      <c r="B55" t="str">
+        <v>khong929@gmail.com</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>6999043000002343375</v>
+      </c>
+      <c r="B56" t="str">
+        <v>halasa@hhsc.ca</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>6999043000002343374</v>
+      </c>
+      <c r="B57" t="str">
+        <v>cmgj11@yahoo.ca</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>6999043000002343373</v>
+      </c>
+      <c r="B58" t="str">
+        <v>jissy.thomas@ahs.ca</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>6999043000002343372</v>
+      </c>
+      <c r="B59" t="str">
+        <v>karine.deshenes@icm-mhi.org</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>6999043000002343371</v>
+      </c>
+      <c r="B60" t="str">
+        <v>cbacher@shn.ca</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>6999043000002343370</v>
+      </c>
+      <c r="B61" t="str">
+        <v>mary.elizabeth.osullivan2@gmail.com</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>6999043000002343369</v>
+      </c>
+      <c r="B62" t="str">
+        <v>janegood@gmail.com</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>6999043000002343368</v>
+      </c>
+      <c r="B63" t="str">
+        <v>shannon.boehr@fraserhealth.ca</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>6999043000002343367</v>
+      </c>
+      <c r="B64" t="str">
+        <v>ian.martel.chum@ssss.gouv.qc.ca</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>6999043000002343366</v>
+      </c>
+      <c r="B65" t="str">
+        <v>ahmadbeigi@hhsc.ca</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>6999043000002343365</v>
+      </c>
+      <c r="B66" t="str">
+        <v>adasilva223@gmail.com</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>6999043000002343364</v>
+      </c>
+      <c r="B67" t="str">
+        <v>veganlelia@gmail.com</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>6999043000002343363</v>
+      </c>
+      <c r="B68" t="str">
+        <v>amandacstimson@gmail.com</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>6999043000002343362</v>
+      </c>
+      <c r="B69" t="str">
+        <v>doctor_sy@yahoo.com</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>6999043000002341154</v>
+      </c>
+      <c r="B70" t="str">
+        <v>aefiander@gmail.com</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>6999043000002341135</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Robertjhmiller@gmail.com</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>6999043000002341132</v>
+      </c>
+      <c r="B72" t="str">
+        <v>jennifer.penner@ahs.ca</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>6999043000002341119</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Kw.dares@gmail.com</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>6999043000002341106</v>
+      </c>
+      <c r="B74" t="str">
+        <v>lorih.penner@saskhealthauthority.ca</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B74"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>email</v>
+      </c>
+      <c r="C1" t="str">
+        <v>original</v>
+      </c>
+      <c r="D1" t="str">
+        <v>truncated</v>
+      </c>
+      <c r="E1" t="str">
+        <v>source</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>6999043000002358171</v>
+      </c>
+      <c r="B2" t="str">
+        <v>mattallen@toh.ca</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Physical Medicine and Rehabilitation - Neuromuscular Medicine</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Physical Medicine and Rehabilitation - Neuromuscul</v>
+      </c>
+      <c r="E2" t="str">
+        <v>SSOT v6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>6999043000002343438</v>
+      </c>
+      <c r="B3" t="str">
+        <v>olivier.desplantie@mail.mcgill.ca</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Cardiology (HF, cardiomyopathies, transplant, cardiac rehab)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Cardiology (HF, cardiomyopathies, transplant, card</v>
+      </c>
+      <c r="E3" t="str">
+        <v>SSOT v6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>6999043000002341177</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Michelle.donais@chudequebec.ca</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Heart failure clinic (Clinique d'insuffisance cardiaque)</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Heart failure clinic (Clinique d'insuffisance card</v>
+      </c>
+      <c r="E4" t="str">
+        <v>SSOT v6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>6999043000002341110</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ahmadamer.ghavanini@thp.ca</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Neurologist and Neuromuscular Disorders Subspecialist</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Neurologist and Neuromuscular Disorders Subspecial</v>
+      </c>
+      <c r="E5" t="str">
+        <v>SSOT v6</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
   </ignoredErrors>
 </worksheet>
 </file>